--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_1_6.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_1_6.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\joyin\workspace\BS-1.9\dev\branches\2.1.2\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HSbank_branches20201013\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7770"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14355" windowHeight="4920"/>
   </bookViews>
   <sheets>
     <sheet name="表1-6 资管产品到期未兑付统计模板" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -34,9 +34,6 @@
   </si>
   <si>
     <t>产品品种：</t>
-  </si>
-  <si>
-    <t>单位：万元，只</t>
   </si>
   <si>
     <t>列编号</t>
@@ -169,6 +166,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>其中：收益权转让产品</t>
@@ -627,6 +625,10 @@
   </si>
   <si>
     <t xml:space="preserve">  产品类型</t>
+  </si>
+  <si>
+    <t>单位：万元，只</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -640,7 +642,7 @@
     <numFmt numFmtId="179" formatCode="0_ "/>
     <numFmt numFmtId="180" formatCode="#,##0.000000_ "/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -652,32 +654,38 @@
       <b/>
       <sz val="16"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="16"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10.5"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -689,6 +697,7 @@
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -699,6 +708,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -707,6 +717,14 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -938,30 +956,54 @@
     <xf numFmtId="180" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -970,30 +1012,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1291,15 +1309,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
+      <c r="A1" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
     </row>
     <row r="2" spans="1:7" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2"/>
@@ -1309,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -1320,125 +1338,125 @@
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="6" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="55" t="s">
-        <v>150</v>
-      </c>
-      <c r="C4" s="55"/>
+      <c r="B4" s="53" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" s="53"/>
       <c r="D4" s="37"/>
       <c r="E4" s="38"/>
-      <c r="F4" s="56" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="57"/>
+      <c r="F4" s="54" t="s">
+        <v>183</v>
+      </c>
+      <c r="G4" s="55"/>
     </row>
     <row r="5" spans="1:7" s="6" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A5" s="34"/>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="56" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="56"/>
+      <c r="D5" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="35" t="s">
+      <c r="E5" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="F5" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="G5" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="35" t="s">
+    </row>
+    <row r="6" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A6" s="57" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A6" s="59" t="s">
+      <c r="B6" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="49" t="s">
+      <c r="C6" s="50"/>
+      <c r="D6" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="50" t="s">
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+    </row>
+    <row r="7" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A7" s="57"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-    </row>
-    <row r="7" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A7" s="59"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49" t="s">
+      <c r="E7" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="52" t="s">
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+    </row>
+    <row r="8" spans="1:7" s="13" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A8" s="57"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-    </row>
-    <row r="8" spans="1:7" s="13" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A8" s="59"/>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="11" t="s">
+      <c r="F8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="G8" s="12" t="s">
         <v>17</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="14" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A9" s="28" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" s="48"/>
       <c r="D9" s="29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A10" s="28" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="48"/>
       <c r="D10" s="15"/>
@@ -1448,126 +1466,126 @@
     </row>
     <row r="11" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A11" s="28" t="s">
-        <v>153</v>
-      </c>
-      <c r="B11" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="43"/>
+        <v>152</v>
+      </c>
+      <c r="B11" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="46"/>
       <c r="D11" s="15"/>
       <c r="E11" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G11" s="30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A12" s="28" t="s">
-        <v>154</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="43"/>
+        <v>153</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="46"/>
       <c r="D12" s="15"/>
       <c r="E12" s="30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F12" s="30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G12" s="30" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A13" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="B13" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="43"/>
+        <v>154</v>
+      </c>
+      <c r="B13" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="46"/>
       <c r="D13" s="15"/>
       <c r="E13" s="30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F13" s="30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G13" s="30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A14" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="B14" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="43"/>
+        <v>155</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="46"/>
       <c r="D14" s="15"/>
       <c r="E14" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G14" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A15" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="B15" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="43"/>
+        <v>156</v>
+      </c>
+      <c r="B15" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="46"/>
       <c r="D15" s="15"/>
       <c r="E15" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G15" s="30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A16" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="B16" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="43"/>
+        <v>157</v>
+      </c>
+      <c r="B16" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="46"/>
       <c r="D16" s="15"/>
       <c r="E16" s="30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G16" s="30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A17" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="B17" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="53"/>
+        <v>158</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="51"/>
       <c r="D17" s="15"/>
       <c r="E17" s="16"/>
       <c r="F17" s="16"/>
@@ -1575,94 +1593,94 @@
     </row>
     <row r="18" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A18" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="B18" s="43" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="43"/>
+        <v>159</v>
+      </c>
+      <c r="B18" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="46"/>
       <c r="D18" s="29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F18" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G18" s="30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A19" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="B19" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="43"/>
+        <v>160</v>
+      </c>
+      <c r="B19" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="46"/>
       <c r="D19" s="29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F19" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G19" s="30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A20" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="B20" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="43"/>
+        <v>161</v>
+      </c>
+      <c r="B20" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="46"/>
       <c r="D20" s="29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G20" s="30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A21" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="B21" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="43"/>
+        <v>176</v>
+      </c>
+      <c r="B21" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="46"/>
       <c r="D21" s="29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F21" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G21" s="30" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A22" s="28" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C22" s="48"/>
       <c r="D22" s="15"/>
@@ -1672,54 +1690,54 @@
     </row>
     <row r="23" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A23" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="B23" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="43"/>
+        <v>178</v>
+      </c>
+      <c r="B23" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="46"/>
       <c r="D23" s="29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F23" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G23" s="30" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A24" s="28" t="s">
-        <v>180</v>
-      </c>
-      <c r="B24" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="43"/>
+        <v>179</v>
+      </c>
+      <c r="B24" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="46"/>
       <c r="D24" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F24" s="30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G24" s="30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A25" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="B25" s="45" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="45"/>
+        <v>180</v>
+      </c>
+      <c r="B25" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="44"/>
       <c r="D25" s="15"/>
       <c r="E25" s="16"/>
       <c r="F25" s="16"/>
@@ -1727,54 +1745,54 @@
     </row>
     <row r="26" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A26" s="28" t="s">
-        <v>176</v>
-      </c>
-      <c r="B26" s="42" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="42"/>
+        <v>175</v>
+      </c>
+      <c r="B26" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="43"/>
       <c r="D26" s="29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E26" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F26" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G26" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A27" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="B27" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="42"/>
+        <v>174</v>
+      </c>
+      <c r="B27" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="43"/>
       <c r="D27" s="29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E27" s="30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F27" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G27" s="30" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A28" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="B28" s="45" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" s="45"/>
+        <v>173</v>
+      </c>
+      <c r="B28" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="44"/>
       <c r="D28" s="15"/>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
@@ -1782,54 +1800,54 @@
     </row>
     <row r="29" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A29" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="B29" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="42"/>
+        <v>172</v>
+      </c>
+      <c r="B29" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="43"/>
       <c r="D29" s="29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E29" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F29" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G29" s="30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A30" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="B30" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="42"/>
+        <v>171</v>
+      </c>
+      <c r="B30" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="43"/>
       <c r="D30" s="29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E30" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F30" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G30" s="30" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A31" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="B31" s="60" t="s">
-        <v>183</v>
-      </c>
-      <c r="C31" s="60"/>
+        <v>170</v>
+      </c>
+      <c r="B31" s="49" t="s">
+        <v>182</v>
+      </c>
+      <c r="C31" s="49"/>
       <c r="D31" s="15"/>
       <c r="E31" s="16"/>
       <c r="F31" s="16"/>
@@ -1837,96 +1855,96 @@
     </row>
     <row r="32" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A32" s="28" t="s">
-        <v>170</v>
-      </c>
-      <c r="B32" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="42"/>
+        <v>169</v>
+      </c>
+      <c r="B32" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="43"/>
       <c r="D32" s="29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E32" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F32" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G32" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A33" s="28" t="s">
-        <v>169</v>
-      </c>
-      <c r="B33" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" s="42"/>
+        <v>168</v>
+      </c>
+      <c r="B33" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="43"/>
       <c r="D33" s="29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E33" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F33" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G33" s="30" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A34" s="28" t="s">
-        <v>168</v>
-      </c>
-      <c r="B34" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="42"/>
+        <v>167</v>
+      </c>
+      <c r="B34" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="43"/>
       <c r="D34" s="29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G34" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A35" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="B35" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="C35" s="42"/>
+        <v>166</v>
+      </c>
+      <c r="B35" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="43"/>
       <c r="D35" s="29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E35" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F35" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G35" s="30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A36" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="B36" s="45" t="s">
-        <v>45</v>
-      </c>
-      <c r="C36" s="45"/>
+        <v>165</v>
+      </c>
+      <c r="B36" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="44"/>
       <c r="D36" s="31"/>
       <c r="E36" s="32"/>
       <c r="F36" s="33"/>
@@ -1934,97 +1952,97 @@
     </row>
     <row r="37" spans="1:7" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="B37" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="C37" s="42"/>
+        <v>164</v>
+      </c>
+      <c r="B37" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="43"/>
       <c r="D37" s="29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F37" s="30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G37" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B38" s="47" t="s">
-        <v>47</v>
-      </c>
-      <c r="C38" s="42"/>
+        <v>46</v>
+      </c>
+      <c r="C38" s="43"/>
       <c r="D38" s="29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E38" s="30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F38" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G38" s="30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="7" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A39" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="B39" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="B39" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" s="45"/>
+      <c r="D39" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="E39" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="F39" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="G39" s="41" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="7" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="C39" s="46"/>
-      <c r="D39" s="40" t="s">
-        <v>71</v>
-      </c>
-      <c r="E39" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="F39" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="G39" s="41" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" s="7" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="44" t="s">
-        <v>49</v>
-      </c>
-      <c r="B40" s="44"/>
-      <c r="C40" s="44"/>
-      <c r="D40" s="44"/>
-      <c r="E40" s="44"/>
-      <c r="F40" s="44"/>
-      <c r="G40" s="44"/>
+      <c r="B40" s="42"/>
+      <c r="C40" s="42"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="42"/>
     </row>
     <row r="41" spans="1:7" s="24" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C41" s="21"/>
       <c r="D41" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F41" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="E41" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>52</v>
-      </c>
       <c r="G41" s="23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -2039,7 +2057,8 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="B6:C8"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="E7:G7"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
@@ -2048,13 +2067,10 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D6:G6"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E7:G7"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B39:C39"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B38:C38"/>
@@ -2065,15 +2081,17 @@
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B39:C39"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="2">

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_1_6.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_1_6.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24701"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HSbank_branches20201013\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\ZGBS-CP\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78914499-D8B7-44D2-9ADD-CC919E1ABD69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14355" windowHeight="4920"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表1-6 资管产品到期未兑付统计模板" sheetId="1" r:id="rId1"/>
@@ -173,9 +174,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">    其中：货币市场基金</t>
-  </si>
-  <si>
     <t xml:space="preserve">注：1.通过下拉选项选择。
     2.各币种折人民币汇率使用报告期最后一个交易日外汇局公布的各币种折人民币汇率中间价。
     3.如果1只产品募集金额既有人民币又有外币，则只数计1只。 
@@ -630,11 +628,15 @@
     <t>单位：万元，只</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve">    其中：货币市场基金或现金管理类产品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="##0"/>
@@ -956,68 +958,68 @@
     <xf numFmtId="180" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
-    <cellStyle name="常规_demo-交叉报表（列标题分为2级）" xfId="2"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规_demo-交叉报表（列标题分为2级）" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1294,32 +1296,32 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultRowHeight="20.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.399999999999999" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="10.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.75" style="25" customWidth="1"/>
-    <col min="4" max="4" width="15.75" style="25" customWidth="1"/>
-    <col min="5" max="5" width="20.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.75" style="27" customWidth="1"/>
-    <col min="7" max="7" width="17.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.77734375" style="25" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" style="25" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.77734375" style="27" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-    </row>
-    <row r="2" spans="1:7" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+    </row>
+    <row r="2" spans="1:7" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1327,53 +1329,53 @@
         <v>0</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="6" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="6" customFormat="1" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="53" t="s">
-        <v>149</v>
-      </c>
-      <c r="C4" s="53"/>
+      <c r="B4" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="43"/>
       <c r="D4" s="37"/>
       <c r="E4" s="38"/>
-      <c r="F4" s="54" t="s">
-        <v>183</v>
-      </c>
-      <c r="G4" s="55"/>
-    </row>
-    <row r="5" spans="1:7" s="6" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="F4" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="G4" s="45"/>
+    </row>
+    <row r="5" spans="1:7" s="6" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A5" s="34"/>
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="56"/>
+      <c r="C5" s="46"/>
       <c r="D5" s="35" t="s">
         <v>6</v>
       </c>
@@ -1387,39 +1389,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A6" s="57" t="s">
+    <row r="6" spans="1:7" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A6" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="50"/>
-      <c r="D6" s="58" t="s">
+      <c r="C6" s="48"/>
+      <c r="D6" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-    </row>
-    <row r="7" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A7" s="57"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+    </row>
+    <row r="7" spans="1:7" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A7" s="47"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="60" t="s">
+      <c r="E7" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-    </row>
-    <row r="8" spans="1:7" s="13" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A8" s="57"/>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+    </row>
+    <row r="8" spans="1:7" s="13" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A8" s="47"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
       <c r="E8" s="11" t="s">
         <v>15</v>
       </c>
@@ -1430,648 +1432,633 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="14" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:7" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="B9" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="54"/>
+      <c r="D9" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="17" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A10" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="B9" s="48" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="48"/>
-      <c r="D9" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="F9" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="G9" s="30" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A10" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="48"/>
+      <c r="C10" s="54"/>
       <c r="D10" s="15"/>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
       <c r="G10" s="16"/>
     </row>
-    <row r="11" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:7" s="17" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="B11" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="B11" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="46"/>
+      <c r="C11" s="53"/>
       <c r="D11" s="15"/>
       <c r="E11" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G11" s="30" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="17" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>153</v>
-      </c>
-      <c r="B12" s="46" t="s">
+        <v>152</v>
+      </c>
+      <c r="B12" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="46"/>
+      <c r="C12" s="53"/>
       <c r="D12" s="15"/>
       <c r="E12" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F12" s="30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G12" s="30" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="17" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
-        <v>154</v>
-      </c>
-      <c r="B13" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="46"/>
+      <c r="C13" s="53"/>
       <c r="D13" s="15"/>
       <c r="E13" s="30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F13" s="30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G13" s="30" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="17" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="B14" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="B14" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="46"/>
+      <c r="C14" s="53"/>
       <c r="D14" s="15"/>
       <c r="E14" s="30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G14" s="30" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="17" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="B15" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="B15" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="46"/>
+      <c r="C15" s="53"/>
       <c r="D15" s="15"/>
       <c r="E15" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G15" s="30" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="17" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="B16" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="B16" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="46"/>
+      <c r="C16" s="53"/>
       <c r="D16" s="15"/>
       <c r="E16" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G16" s="30" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="18" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="B17" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="B17" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="51"/>
+      <c r="C17" s="55"/>
       <c r="D17" s="15"/>
       <c r="E17" s="16"/>
       <c r="F17" s="16"/>
       <c r="G17" s="16"/>
     </row>
-    <row r="18" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:7" s="17" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="B18" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="53"/>
+      <c r="D18" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="G18" s="30" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="17" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="B18" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="46"/>
-      <c r="D18" s="29" t="s">
+      <c r="B19" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="53"/>
+      <c r="D19" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E19" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="F18" s="30" t="s">
+      <c r="F19" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="G18" s="30" t="s">
+      <c r="G19" s="30" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A19" s="28" t="s">
+    <row r="20" spans="1:7" s="17" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="B19" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="46"/>
-      <c r="D19" s="29" t="s">
+      <c r="B20" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="53"/>
+      <c r="D20" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="30" t="s">
+      <c r="E20" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="F19" s="30" t="s">
+      <c r="F20" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="G19" s="30" t="s">
+      <c r="G20" s="30" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A20" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="B20" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="46"/>
-      <c r="D20" s="29" t="s">
+    <row r="21" spans="1:7" s="17" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A21" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="B21" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="53"/>
+      <c r="D21" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="30" t="s">
+      <c r="E21" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="F20" s="30" t="s">
+      <c r="F21" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="G20" s="30" t="s">
+      <c r="G21" s="30" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A21" s="28" t="s">
+    <row r="22" spans="1:7" s="17" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A22" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="B21" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="46"/>
-      <c r="D21" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="F21" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="G21" s="30" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A22" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="B22" s="48" t="s">
+      <c r="B22" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="48"/>
+      <c r="C22" s="54"/>
       <c r="D22" s="15"/>
       <c r="E22" s="16"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
     </row>
-    <row r="23" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:7" s="17" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="B23" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="53"/>
+      <c r="D23" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" s="30" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="17" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A24" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="B23" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="46"/>
-      <c r="D23" s="29" t="s">
+      <c r="B24" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="53"/>
+      <c r="D24" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="E23" s="30" t="s">
+      <c r="E24" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="F23" s="30" t="s">
+      <c r="F24" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="G23" s="30" t="s">
+      <c r="G24" s="30" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A24" s="28" t="s">
+    <row r="25" spans="1:7" s="17" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="B24" s="46" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="F24" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="G24" s="30" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A25" s="28" t="s">
-        <v>180</v>
-      </c>
-      <c r="B25" s="44" t="s">
+      <c r="B25" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="44"/>
+      <c r="C25" s="58"/>
       <c r="D25" s="15"/>
       <c r="E25" s="16"/>
       <c r="F25" s="16"/>
       <c r="G25" s="16"/>
     </row>
-    <row r="26" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:7" s="17" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="B26" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="B26" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="43"/>
+      <c r="C26" s="52"/>
       <c r="D26" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="F26" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="G26" s="30" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" s="17" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A27" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="B27" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="52"/>
+      <c r="D27" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="E26" s="30" t="s">
+      <c r="E27" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="F26" s="30" t="s">
+      <c r="F27" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="G26" s="30" t="s">
+      <c r="G27" s="30" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="17" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A27" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="B27" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="43"/>
-      <c r="D27" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="E27" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="F27" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="G27" s="30" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:7" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="B28" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="C28" s="44"/>
+      <c r="C28" s="58"/>
       <c r="D28" s="15"/>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
       <c r="G28" s="16"/>
     </row>
-    <row r="29" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:7" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="B29" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="B29" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="43"/>
+      <c r="C29" s="52"/>
       <c r="D29" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="E29" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="G29" s="30" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A30" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="B30" s="52" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="52"/>
+      <c r="D30" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="E29" s="30" t="s">
+      <c r="E30" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="F29" s="30" t="s">
+      <c r="F30" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="G29" s="30" t="s">
+      <c r="G30" s="30" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A30" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="B30" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="43"/>
-      <c r="D30" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="E30" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="F30" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="G30" s="30" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:7" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A31" s="28" t="s">
-        <v>170</v>
-      </c>
-      <c r="B31" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="C31" s="49"/>
+        <v>169</v>
+      </c>
+      <c r="B31" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="C31" s="57"/>
       <c r="D31" s="15"/>
       <c r="E31" s="16"/>
       <c r="F31" s="16"/>
       <c r="G31" s="16"/>
     </row>
-    <row r="32" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:7" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
-        <v>169</v>
-      </c>
-      <c r="B32" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="B32" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="43"/>
+      <c r="C32" s="52"/>
       <c r="D32" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="G32" s="30" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A33" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="B33" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="52"/>
+      <c r="D33" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="E32" s="30" t="s">
+      <c r="E33" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="F32" s="30" t="s">
+      <c r="F33" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="G32" s="30" t="s">
+      <c r="G33" s="30" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A33" s="28" t="s">
-        <v>168</v>
-      </c>
-      <c r="B33" s="43" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="43"/>
-      <c r="D33" s="29" t="s">
+    <row r="34" spans="1:7" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A34" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="B34" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="52"/>
+      <c r="D34" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="E33" s="30" t="s">
+      <c r="E34" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="F33" s="30" t="s">
+      <c r="F34" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="G33" s="30" t="s">
+      <c r="G34" s="30" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A34" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="B34" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="43"/>
-      <c r="D34" s="29" t="s">
+    <row r="35" spans="1:7" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A35" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="B35" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="52"/>
+      <c r="D35" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="E34" s="30" t="s">
+      <c r="E35" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="F34" s="30" t="s">
+      <c r="F35" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="G34" s="30" t="s">
+      <c r="G35" s="30" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A35" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="B35" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="43"/>
-      <c r="D35" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="E35" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="F35" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="G35" s="30" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:7" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="B36" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="B36" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="44"/>
+      <c r="C36" s="58"/>
       <c r="D36" s="31"/>
       <c r="E36" s="32"/>
       <c r="F36" s="33"/>
       <c r="G36" s="16"/>
     </row>
-    <row r="37" spans="1:7" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:7" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="B37" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="B37" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="43"/>
+      <c r="C37" s="52"/>
       <c r="D37" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="E37" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="F37" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="G37" s="30" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="52"/>
+      <c r="D38" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="E37" s="30" t="s">
+      <c r="E38" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="F37" s="30" t="s">
+      <c r="F38" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="G37" s="30" t="s">
+      <c r="G38" s="30" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="B38" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="43"/>
-      <c r="D38" s="29" t="s">
+    <row r="39" spans="1:7" s="7" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="B39" s="60" t="s">
+        <v>183</v>
+      </c>
+      <c r="C39" s="60"/>
+      <c r="D39" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="E38" s="30" t="s">
+      <c r="E39" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="F38" s="30" t="s">
+      <c r="F39" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="G38" s="30" t="s">
+      <c r="G39" s="41" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="7" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="B39" s="45" t="s">
+    <row r="40" spans="1:7" s="7" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="C39" s="45"/>
-      <c r="D39" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="E39" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="F39" s="41" t="s">
-        <v>118</v>
-      </c>
-      <c r="G39" s="41" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" s="7" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="42" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="42"/>
-      <c r="C40" s="42"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="42"/>
+      <c r="B40" s="59"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
     </row>
     <row r="41" spans="1:7" s="24" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C41" s="21"/>
       <c r="D41" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="F41" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E41" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>51</v>
-      </c>
       <c r="G41" s="23" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="F42" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:C8"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B18:C18"/>
@@ -2086,17 +2073,32 @@
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:C8"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="D7:D8"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A5:G5"/>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="B4:C4">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A5:G5" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="B4:C4" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"--,01-银行非保本理财,02-信托公司资管产品,03-证券公司及其子公司资管产品,04-基金管理公司及其子公司专户,05-期货公司及其子公司资管产品,06-保险资管产品,07-金融资产投资公司资管产品,08-公募基金"</formula1>
     </dataValidation>
   </dataValidations>
